--- a/assets/translations/Japanese.Japan.ja-JP.xlsx
+++ b/assets/translations/Japanese.Japan.ja-JP.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shigekazu HIguchi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C58667-BD17-4CA3-8A4B-DE8A131E49F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB1950-D7A6-4A41-B399-F2FF1F9C6EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10040" yWindow="2680" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
     <sheet name="Statements" sheetId="1" r:id="rId2"/>
     <sheet name="Key messages" sheetId="4" r:id="rId3"/>
+    <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="212">
   <si>
     <t>Number</t>
   </si>
@@ -1334,7 +1335,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -1344,7 +1345,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
@@ -1381,7 +1382,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -1551,7 +1552,7 @@
       <rPr>
         <strike/>
         <sz val="12"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -1561,7 +1562,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="游ゴシック"/>
+        <rFont val="Calibri"/>
         <family val="3"/>
         <charset val="128"/>
         <scheme val="minor"/>
@@ -1623,16 +1624,46 @@
     </rPh>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Consensus statements</t>
+  </si>
+  <si>
+    <t>章</t>
+  </si>
+  <si>
+    <t>陳述</t>
+  </si>
+  <si>
+    <t>簡略化された陳述</t>
+  </si>
+  <si>
+    <t>文脈情報</t>
+  </si>
+  <si>
+    <t>参考文献</t>
+  </si>
+  <si>
+    <t>Consensus statements (Japanese)</t>
+  </si>
+  <si>
+    <t>Key messages</t>
+  </si>
+  <si>
+    <t>重要なメッセージ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1671,7 +1702,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -1680,7 +1711,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -1693,13 +1724,13 @@
     <font>
       <sz val="15"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -1720,64 +1751,87 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック Light"/>
+      <name val="Calibri Light"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック Light"/>
+      <name val="Calibri Light"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <strike/>
       <sz val="12"/>
-      <name val="游ゴシック"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color theme="9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1795,7 +1849,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1849,21 +1903,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1956,17 +1995,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1976,11 +2004,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1990,16 +2020,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
@@ -2007,22 +2037,22 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2031,47 +2061,46 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="2" xr:uid="{EA2286F0-4419-DD46-B562-27818B6B815A}"/>
+    <cellStyle name="Standard 3" xfId="3" xr:uid="{CB50FD64-A163-7E4B-8EC9-9C21E7A480FC}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2389,17 +2418,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="10.77734375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24.33203125" style="2" customWidth="1"/>
-    <col min="2" max="3" width="21.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="42.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="10.77734375" style="2"/>
+    <col min="2" max="3" width="21.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="42.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
@@ -2420,7 +2449,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" s="11" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" s="11" customFormat="1">
       <c r="A2" s="11" t="s">
         <v>31</v>
       </c>
@@ -2440,7 +2469,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="11" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" s="11" customFormat="1">
       <c r="A3" s="11" t="s">
         <v>36</v>
       </c>
@@ -2460,8 +2489,8 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:7" s="11" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" s="11" customFormat="1"/>
+    <row r="5" spans="1:7" s="11" customFormat="1">
       <c r="D5" s="9"/>
     </row>
   </sheetData>
@@ -2477,800 +2506,881 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:J27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="49.6640625" customWidth="1"/>
-    <col min="2" max="2" width="25.109375" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="42.33203125" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" customWidth="1"/>
-    <col min="7" max="7" width="42.33203125" style="23" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" customWidth="1"/>
-    <col min="9" max="9" width="42.33203125" style="32" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" customWidth="1"/>
+    <col min="3" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="42.33203125" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="42.33203125" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="42.33203125" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>5</v>
+      <c r="B1" t="s">
+        <v>204</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="26" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" s="10" customFormat="1" ht="78" x14ac:dyDescent="0.4">
+      <c r="J1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" s="10" customFormat="1" ht="85">
       <c r="A2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="F2" s="16" t="s">
         <v>182</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="H2" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="I2" s="27" t="s">
+      <c r="J2" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" ht="85">
       <c r="A3" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5">
+        <v>2</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="25" t="s">
+      <c r="H3" s="23" t="s">
         <v>122</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="I3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="J3" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" ht="119">
       <c r="A4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="H4" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="26" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="94.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" ht="94.5" customHeight="1">
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C5" s="5">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5">
+        <v>4</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="F5" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="I5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="J5" s="27" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" ht="119">
       <c r="A6" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="F6" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="H6" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="I6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="J6" s="24" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" ht="68">
       <c r="A7" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C7" s="5">
         <v>6</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="F7" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="I7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="J7" s="27" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" ht="87">
       <c r="A8" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="5">
         <v>7</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="F8" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="H8" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="I8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="J8" s="24" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" ht="85">
       <c r="A9" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C9" s="5">
         <v>8</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="F9" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="H9" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="I9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="J9" s="27" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="39" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" ht="51">
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C10" s="5">
         <v>9</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="F10" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="H10" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="I10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="J10" s="24" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="69.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" ht="69.75" customHeight="1">
       <c r="A11" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="5">
         <v>10</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5">
+        <v>10</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="F11" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="H11" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="I11" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="J11" s="27" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="97.5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" ht="102">
       <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="5">
         <v>11</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="F12" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="H12" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="I12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="J12" s="24" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" ht="51">
       <c r="A13" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="5">
         <v>12</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5">
+        <v>12</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="F13" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="H13" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="I13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="I13" s="30" t="s">
+      <c r="J13" s="27" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="45" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" ht="51">
       <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="5">
         <v>13</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5">
+        <v>13</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="F14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="H14" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="J14" s="27" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="78" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" ht="85">
       <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C15" s="5">
         <v>14</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="F15" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="H15" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="I15" s="30" t="s">
+      <c r="J15" s="27" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="59.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" ht="59.25" customHeight="1">
       <c r="A16" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="5">
         <v>15</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="F16" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="H16" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="I16" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="I16" s="27" t="s">
+      <c r="J16" s="24" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="60" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" ht="68">
       <c r="A17" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C17" s="5">
         <v>16</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="F17" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="H17" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="I17" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I17" s="27" t="s">
+      <c r="J17" s="24" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:10" ht="51">
       <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C18" s="5">
         <v>17</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5">
+        <v>17</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="F18" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="H18" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I18" s="30" t="s">
+      <c r="J18" s="27" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:10" ht="68">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C19" s="5">
         <v>18</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5">
+        <v>18</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="F19" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="H19" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I19" s="27" t="s">
+      <c r="J19" s="24" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" ht="68">
       <c r="A20" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="5">
         <v>19</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5">
+        <v>19</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="F20" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="H20" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="I20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="27" t="s">
+      <c r="J20" s="24" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="60" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" ht="68">
       <c r="A21" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="5">
         <v>20</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="F21" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="H21" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="I21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I21" s="27" t="s">
+      <c r="J21" s="24" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="58.5" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" ht="68">
       <c r="A22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="5">
         <v>21</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5">
+        <v>21</v>
+      </c>
+      <c r="E22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="F22" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="H22" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="I22" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="I22" s="27" t="s">
+      <c r="J22" s="24" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="69" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:10" ht="69" customHeight="1">
       <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="5">
         <v>22</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="5">
+        <v>22</v>
+      </c>
+      <c r="E23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="F23" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="H23" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="I23" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="I23" s="27" t="s">
+      <c r="J23" s="24" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" ht="63.75" customHeight="1">
       <c r="A24" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C24" s="5">
         <v>23</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5">
+        <v>23</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="F24" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="H24" s="18" t="s">
         <v>198</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="I24" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="I24" s="30" t="s">
+      <c r="J24" s="27" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="55.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:10" ht="55.5" customHeight="1">
       <c r="A25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="5">
         <v>24</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5">
+        <v>24</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="F25" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="H25" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="I25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="30" t="s">
+      <c r="J25" s="27" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="105" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:10" ht="105" customHeight="1">
       <c r="A26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="B26" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="5">
         <v>25</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5">
+        <v>25</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="F26" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="H26" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="I26" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="I26" s="27" t="s">
+      <c r="J26" s="24" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="122.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" ht="122.25" customHeight="1" thickBot="1">
       <c r="A27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C27" s="7">
         <v>26</v>
       </c>
-      <c r="D27" s="8" t="s">
+      <c r="D27" s="7">
+        <v>26</v>
+      </c>
+      <c r="E27" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="F27" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="G27" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G27" s="22" t="s">
+      <c r="H27" s="20" t="s">
         <v>170</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="I27" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="31" t="s">
+      <c r="J27" s="28" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3282,14 +3392,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A98B4A3-5095-AF4B-B22C-B7631D8C258B}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="19.5" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" customWidth="1"/>
+    <col min="2" max="2" width="32.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="13" t="s">
         <v>30</v>
       </c>
@@ -3297,43 +3407,51 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="123.75" x14ac:dyDescent="0.5">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:2" ht="21">
+      <c r="A2" s="32" t="s">
+        <v>210</v>
+      </c>
+      <c r="B2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="105">
+      <c r="A3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="74.25" x14ac:dyDescent="0.5">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:2" ht="63">
+      <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="99" x14ac:dyDescent="0.5">
-      <c r="A4" s="13" t="s">
+    <row r="5" spans="1:2" ht="84">
+      <c r="A5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="99" x14ac:dyDescent="0.5">
-      <c r="A5" s="13" t="s">
+    <row r="6" spans="1:2" ht="84">
+      <c r="A6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="99" x14ac:dyDescent="0.5">
-      <c r="A6" s="13" t="s">
+    <row r="7" spans="1:2" ht="84">
+      <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>178</v>
       </c>
     </row>
@@ -3342,4 +3460,43 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4A91D82-FE75-D142-AF2B-8B22F3ECE84F}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="24.5" style="30" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="30" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assets/translations/Japanese.Japan.ja-JP.xlsx
+++ b/assets/translations/Japanese.Japan.ja-JP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/Repos_Misc/2024-04_Ladenburg_Roundtable/LCS/assets/translations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB1950-D7A6-4A41-B399-F2FF1F9C6EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8AE762C-1072-6F44-99B0-C1FEB2E2EB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10040" yWindow="2680" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21440" yWindow="4280" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Contributors" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="213">
   <si>
     <t>Number</t>
   </si>
@@ -1183,149 +1183,6 @@
   </si>
   <si>
     <t>Light is a powerful signal for the body as it affects our circadian rhythms, sleep, mood, and cognitive performance.</t>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>夕方の低い光量と睡眠中の暗闇は、健康的な明暗リズムの一部です。</t>
-    <rPh sb="0" eb="2">
-      <t>ユウガタ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>ヒク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>コウリョウ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>スイミンチュウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>クラヤミ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>ケンコウテキ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>メイアン</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>イチブ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>光曝露を管理することは、食事や運動、睡眠衛生と同様に、健康的なライフスタイルの一部です。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>バクロ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ショクジ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ウンドウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>スイミン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>エイセイ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ドウヨウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>ケンコウ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>テキ</t>
-    </rPh>
-    <rPh sb="39" eb="41">
-      <t>イチブ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>光がどのくらい明るいかだけではなく、「いつ」、「どのような種類」の光かが重要です。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>アカ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="36" eb="38">
-      <t>ジュウヨウ</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>光は、概日リズムや睡眠、気分、認知機能に影響を与える、生体にとっての強力なシグナルです。</t>
-    <rPh sb="0" eb="1">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ガイジツ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>スイミン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>キブン</t>
-    </rPh>
-    <rPh sb="15" eb="19">
-      <t>ニンチキノウ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>エイキョウ</t>
-    </rPh>
-    <rPh sb="23" eb="24">
-      <t>アタ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>セイタイ</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>キョウリョク</t>
-    </rPh>
-    <phoneticPr fontId="10"/>
-  </si>
-  <si>
-    <t>朝や日中の光は健康をサポートしますが、夜の光は健康を乱すことがあります。</t>
-    <rPh sb="0" eb="1">
-      <t>アサ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニッチュウ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ケンコウ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ヨル</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ヒカリ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ケンコウ</t>
-    </rPh>
-    <rPh sb="26" eb="27">
-      <t>ミダ</t>
-    </rPh>
     <phoneticPr fontId="10"/>
   </si>
   <si>
@@ -1634,15 +1491,6 @@
     <t>章</t>
   </si>
   <si>
-    <t>陳述</t>
-  </si>
-  <si>
-    <t>簡略化された陳述</t>
-  </si>
-  <si>
-    <t>文脈情報</t>
-  </si>
-  <si>
     <t>参考文献</t>
   </si>
   <si>
@@ -1653,13 +1501,171 @@
   </si>
   <si>
     <t>重要なメッセージ</t>
+  </si>
+  <si>
+    <r>
+      <t>光は、概日リズムや睡眠、気分、認知機能に影響を与える、生体にとっての強力な</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>シグナル</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>です。</t>
+    </r>
+  </si>
+  <si>
+    <t>光がどのくらい明るいかだけではなく、「いつ」、「どのような種類」の光かが重要です。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>アカ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ジュウヨウ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>朝や日中の光は健康をサポートしますが、夜の光は健康を</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>乱すことがあります。</t>
+    </r>
+  </si>
+  <si>
+    <t>夕方の低い光量と睡眠中の暗闇は、健康的な明暗リズムの一部です。</t>
+    <rPh sb="0" eb="2">
+      <t>ユウガタ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>コウリョウ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>スイミンチュウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>クラヤミ</t>
+    </rPh>
+    <rPh sb="16" eb="19">
+      <t>ケンコウテキ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>メイアン</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>光曝露を管理することは、食事や運動、睡眠衛生と同様に、健康的なライフスタイルの一部です。</t>
+    <rPh sb="0" eb="1">
+      <t>ヒカリ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>バクロ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ショクジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ウンドウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>スイミン</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>エイセイ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ドウヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イチブ</t>
+    </rPh>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>No.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>声明</t>
+    <rPh sb="0" eb="2">
+      <t>ｾｲﾒｲ</t>
+    </rPh>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>簡潔な声明</t>
+    <rPh sb="0" eb="2">
+      <t>ｶﾝｹﾂ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ｾｲﾒｲ</t>
+    </rPh>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景情報</t>
+    <rPh sb="0" eb="2">
+      <t>ﾊｲｹｲ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ｼﾞｮｳﾎｳ</t>
+    </rPh>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1741,13 +1747,6 @@
       <color rgb="FF242424"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
@@ -1834,6 +1833,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1849,7 +1877,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2003,14 +2031,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2049,52 +2092,63 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -2513,11 +2567,11 @@
     <col min="2" max="2" width="25.1640625" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="42.33203125" customWidth="1"/>
-    <col min="6" max="6" width="42.33203125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="20" customWidth="1"/>
     <col min="7" max="7" width="42.33203125" customWidth="1"/>
-    <col min="8" max="8" width="42.33203125" style="21" customWidth="1"/>
+    <col min="8" max="8" width="42.33203125" style="20" customWidth="1"/>
     <col min="9" max="9" width="42.33203125" customWidth="1"/>
-    <col min="10" max="10" width="42.33203125" style="29" customWidth="1"/>
+    <col min="10" max="10" width="42.33203125" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="17">
@@ -2525,31 +2579,31 @@
         <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="33" t="s">
-        <v>208</v>
+      <c r="D1" s="34" t="s">
+        <v>209</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F1" t="s">
-        <v>205</v>
+      <c r="F1" s="35" t="s">
+        <v>210</v>
       </c>
       <c r="G1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
-        <v>206</v>
+      <c r="H1" s="35" t="s">
+        <v>211</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J1" t="s">
-        <v>207</v>
+      <c r="J1" s="36" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="10" customFormat="1" ht="85">
@@ -2568,19 +2622,19 @@
       <c r="E2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>182</v>
+      <c r="F2" s="15" t="s">
+        <v>177</v>
       </c>
       <c r="G2" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="21" t="s">
         <v>138</v>
       </c>
       <c r="I2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="J2" s="24" t="s">
+      <c r="J2" s="23" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2600,19 +2654,19 @@
       <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="22" t="s">
         <v>122</v>
       </c>
       <c r="I3" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="24" t="s">
         <v>97</v>
       </c>
     </row>
@@ -2632,19 +2686,19 @@
       <c r="E4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>183</v>
+      <c r="F4" s="16" t="s">
+        <v>178</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="18" t="s">
+      <c r="H4" s="17" t="s">
         <v>123</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="J4" s="26" t="s">
+      <c r="J4" s="25" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2664,19 +2718,19 @@
       <c r="E5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>142</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="17" t="s">
         <v>124</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="27" t="s">
+      <c r="J5" s="26" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2696,20 +2750,20 @@
       <c r="E6" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="18" t="s">
         <v>136</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="17" t="s">
         <v>125</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="24" t="s">
-        <v>199</v>
+      <c r="J6" s="23" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="68">
@@ -2728,19 +2782,19 @@
       <c r="E7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="17" t="s">
         <v>143</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="17" t="s">
         <v>144</v>
       </c>
       <c r="I7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="26" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2760,19 +2814,19 @@
       <c r="E8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="17" t="s">
         <v>145</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="17" t="s">
         <v>146</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2792,19 +2846,19 @@
       <c r="E9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="17" t="s">
         <v>148</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="17" t="s">
         <v>149</v>
       </c>
       <c r="I9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="26" t="s">
         <v>127</v>
       </c>
     </row>
@@ -2824,19 +2878,19 @@
       <c r="E10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="17" t="s">
         <v>150</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="H10" s="17" t="s">
         <v>151</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="23" t="s">
         <v>152</v>
       </c>
     </row>
@@ -2856,19 +2910,19 @@
       <c r="E11" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="17" t="s">
         <v>153</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="17" t="s">
         <v>171</v>
       </c>
       <c r="I11" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="27" t="s">
+      <c r="J11" s="26" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2888,19 +2942,19 @@
       <c r="E12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="17" t="s">
         <v>154</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H12" s="18" t="s">
+      <c r="H12" s="17" t="s">
         <v>155</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="23" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2920,19 +2974,19 @@
       <c r="E13" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="17" t="s">
         <v>172</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="18" t="s">
+      <c r="H13" s="17" t="s">
         <v>173</v>
       </c>
       <c r="I13" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>128</v>
       </c>
     </row>
@@ -2952,19 +3006,19 @@
       <c r="E14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="18" t="s">
+      <c r="F14" s="17" t="s">
         <v>58</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="H14" s="18" t="s">
+      <c r="H14" s="17" t="s">
         <v>157</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="26" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2984,19 +3038,19 @@
       <c r="E15" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="18" t="s">
-        <v>184</v>
+      <c r="F15" s="17" t="s">
+        <v>179</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="18" t="s">
-        <v>191</v>
+      <c r="H15" s="17" t="s">
+        <v>186</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="26" t="s">
         <v>158</v>
       </c>
     </row>
@@ -3016,19 +3070,19 @@
       <c r="E16" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="F16" s="18" t="s">
-        <v>185</v>
+      <c r="F16" s="17" t="s">
+        <v>180</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="18" t="s">
-        <v>192</v>
+      <c r="H16" s="17" t="s">
+        <v>187</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J16" s="24" t="s">
+      <c r="J16" s="23" t="s">
         <v>159</v>
       </c>
     </row>
@@ -3048,19 +3102,19 @@
       <c r="E17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="18" t="s">
+      <c r="F17" s="17" t="s">
         <v>160</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="H17" s="18" t="s">
-        <v>193</v>
+      <c r="H17" s="17" t="s">
+        <v>188</v>
       </c>
       <c r="I17" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="24" t="s">
+      <c r="J17" s="23" t="s">
         <v>161</v>
       </c>
     </row>
@@ -3080,19 +3134,19 @@
       <c r="E18" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="18" t="s">
-        <v>186</v>
+      <c r="F18" s="17" t="s">
+        <v>181</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H18" s="18" t="s">
-        <v>194</v>
+      <c r="H18" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="I18" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="27" t="s">
+      <c r="J18" s="26" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3112,20 +3166,20 @@
       <c r="E19" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="18" t="s">
-        <v>187</v>
+      <c r="F19" s="17" t="s">
+        <v>182</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="H19" s="18" t="s">
+      <c r="H19" s="17" t="s">
         <v>175</v>
       </c>
       <c r="I19" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="J19" s="24" t="s">
-        <v>200</v>
+      <c r="J19" s="23" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="68">
@@ -3144,19 +3198,19 @@
       <c r="E20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F20" s="18" t="s">
-        <v>188</v>
+      <c r="F20" s="17" t="s">
+        <v>183</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H20" s="18" t="s">
-        <v>195</v>
+      <c r="H20" s="17" t="s">
+        <v>190</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="23" t="s">
         <v>162</v>
       </c>
     </row>
@@ -3176,19 +3230,19 @@
       <c r="E21" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F21" s="18" t="s">
-        <v>189</v>
+      <c r="F21" s="17" t="s">
+        <v>184</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="18" t="s">
-        <v>196</v>
+      <c r="H21" s="17" t="s">
+        <v>191</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="J21" s="24" t="s">
+      <c r="J21" s="23" t="s">
         <v>163</v>
       </c>
     </row>
@@ -3208,19 +3262,19 @@
       <c r="E22" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>174</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H22" s="18" t="s">
+      <c r="H22" s="17" t="s">
         <v>130</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="24" t="s">
+      <c r="J22" s="23" t="s">
         <v>164</v>
       </c>
     </row>
@@ -3240,20 +3294,20 @@
       <c r="E23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F23" s="18" t="s">
-        <v>190</v>
+      <c r="F23" s="17" t="s">
+        <v>185</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="18" t="s">
-        <v>197</v>
+      <c r="H23" s="17" t="s">
+        <v>192</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="J23" s="24" t="s">
-        <v>201</v>
+      <c r="J23" s="23" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="63.75" customHeight="1">
@@ -3272,19 +3326,19 @@
       <c r="E24" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>198</v>
+      <c r="H24" s="17" t="s">
+        <v>193</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="J24" s="27" t="s">
+      <c r="J24" s="26" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3304,19 +3358,19 @@
       <c r="E25" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>165</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="H25" s="18" t="s">
+      <c r="H25" s="17" t="s">
         <v>166</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="J25" s="27" t="s">
+      <c r="J25" s="26" t="s">
         <v>140</v>
       </c>
     </row>
@@ -3336,19 +3390,19 @@
       <c r="E26" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="17" t="s">
         <v>167</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H26" s="18" t="s">
+      <c r="H26" s="17" t="s">
         <v>132</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="J26" s="24" t="s">
+      <c r="J26" s="23" t="s">
         <v>168</v>
       </c>
     </row>
@@ -3368,19 +3422,19 @@
       <c r="E27" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="F27" s="19" t="s">
         <v>169</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="20" t="s">
+      <c r="H27" s="19" t="s">
         <v>170</v>
       </c>
       <c r="I27" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="J27" s="28" t="s">
+      <c r="J27" s="27" t="s">
         <v>121</v>
       </c>
     </row>
@@ -3408,51 +3462,51 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="21">
-      <c r="A2" s="32" t="s">
-        <v>210</v>
+      <c r="A2" s="31" t="s">
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="105">
       <c r="A3" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>180</v>
+      <c r="B3" s="32" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="63">
       <c r="A4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>179</v>
+      <c r="B4" s="33" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="84">
       <c r="A5" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>181</v>
+      <c r="B5" s="33" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="84">
       <c r="A6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>177</v>
+      <c r="B6" s="33" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="84">
       <c r="A7" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>178</v>
+      <c r="B7" s="33" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3467,33 +3521,33 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="24.5" style="30" customWidth="1"/>
-    <col min="2" max="2" width="27.1640625" style="30" customWidth="1"/>
-    <col min="3" max="16384" width="11" style="30"/>
+    <col min="1" max="1" width="24.5" style="29" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" style="29" customWidth="1"/>
+    <col min="3" max="16384" width="11" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="29" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="30" t="s">
-        <v>203</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>209</v>
+      <c r="A2" s="29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="30" t="s">
-        <v>202</v>
-      </c>
-      <c r="B3" s="31" t="s">
-        <v>208</v>
+      <c r="A3" s="29" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
